--- a/mlef_pipeline/results/DCR/SQUAMOUS/RWD_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/RWD_PYRAD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.55 ± 0.12</t>
+          <t>0.56 ± 0.09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.23</t>
+          <t>0.61 ± 0.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.28</t>
+          <t>0.60 ± 0.26</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.51 ± 0.21</t>
+          <t>0.50 ± 0.21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
